--- a/output/pdf_financials_xlsx/PALI.xlsx
+++ b/output/pdf_financials_xlsx/PALI.xlsx
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.369846</v>
+        <v>259.379364</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.035767</v>
+        <v>164.690559</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.167014</v>
+        <v>52.16657</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.050419</v>
+        <v>92.429</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>29.91</v>
       </c>
     </row>
     <row r="11">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.167014</v>
+        <v>-52.16657</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.050419</v>
+        <v>-92.429</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-29.91</v>
       </c>
     </row>
     <row r="12">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.269047</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.073936</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.06952999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="13">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>361.398126</v>
+        <v>361.129079</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-206.957671</v>
+        <v>-207.031607</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-63.043808</v>
+        <v>-63.113338</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-110.099</v>
+        <v>-110.108</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>207.791</v>
+        <v>207.735</v>
       </c>
     </row>
     <row r="28">
@@ -1075,19 +1075,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>361.634961</v>
+        <v>361.365914</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-206.957671</v>
+        <v>-207.031607</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-63.043808</v>
+        <v>-63.113338</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-110.099</v>
+        <v>-110.108</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>207.795</v>
+        <v>207.739</v>
       </c>
     </row>
     <row r="30">
@@ -1199,10 +1199,10 @@
         <v>0.838113</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.207497</v>
+        <v>0.207</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="35">
@@ -1243,10 +1243,10 @@
         <v>0.838113</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.207497</v>
+        <v>0.207</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="37">
@@ -1507,10 +1507,10 @@
         <v>7.743321</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.125503</v>
+        <v>4.126</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>215.552</v>
+        <v>214.283</v>
       </c>
     </row>
     <row r="49">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">

--- a/output/pdf_financials_xlsx/PALI.xlsx
+++ b/output/pdf_financials_xlsx/PALI.xlsx
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-3.511843</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -5915,7 +5915,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -6989,7 +6993,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7295,7 +7303,11 @@
           <t>Re-purchase of common shares</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -7617,7 +7629,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
         <v>103.568843</v>
       </c>
